--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260918.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.09%</t>
+          <t>11.45%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.37%</t>
+          <t>10.49%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.64%</t>
+          <t>7.85%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>7.82%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.46%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>4.52%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,431</t>
+          <t>135,701</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>135,701</t>
+          <t>22,431</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>30,114</t>
+          <t>11,237</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,237</t>
+          <t>30,114</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1386,51 +1386,51 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>145,345</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>145,345</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1496,51 +1496,51 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>13,324</t>
+          <t>94,102</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>94,102</t>
+          <t>13,324</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>137,799,120</t>
+          <t>137,555,241</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
